--- a/data/trans_orig/P39B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023</t>
+          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30880</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388924</t>
+          <t>389280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>416686</t>
+          <t>416566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>599041</t>
+          <t>599752</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>624617</t>
+          <t>625068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>999025</t>
+          <t>996544</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1034086</t>
+          <t>1034333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>31372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53184</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>36477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55466</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>73439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101930</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,47 +1540,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14648</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23121</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14648</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8975</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23628</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49693</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2125121</t>
+          <t>2126054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2187795</t>
+          <t>2186118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2108046</t>
+          <t>2105424</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2153261</t>
+          <t>2148939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4244521</t>
+          <t>4240351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4320259</t>
+          <t>4318730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>33586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>69189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59241</t>
+          <t>59131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72258</t>
+          <t>72045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117151</t>
+          <t>118712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,82 +2109,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11057</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>14236</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>23863</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5916</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2771</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10816</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>14236</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8222</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>22725</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>607610</t>
+          <t>608077</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>627247</t>
+          <t>628689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>624792</t>
+          <t>623751</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>642551</t>
+          <t>642730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1240032</t>
+          <t>1239926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1266999</t>
+          <t>1266668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41123</t>
+          <t>41577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41317</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>46966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74743</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46466</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83480</t>
+          <t>82613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3142167</t>
+          <t>3144587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3221617</t>
+          <t>3227045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3349306</t>
+          <t>3346737</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3413407</t>
+          <t>3409823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6509758</t>
+          <t>6506203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6613026</t>
+          <t>6607123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75276</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122274</t>
+          <t>120299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69439</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107908</t>
+          <t>109422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160185</t>
+          <t>159120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221416</t>
+          <t>218560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62068</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60634</t>
+          <t>60608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98258</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>404385</t>
+          <t>448545</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>389280</t>
+          <t>431760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>416566</t>
+          <t>462792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>613131</t>
+          <t>665638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>599752</t>
+          <t>652206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>625068</t>
+          <t>677558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1017516</t>
+          <t>1114183</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>996544</t>
+          <t>1093150</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1034333</t>
+          <t>1133726</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>47580</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>49593</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>86780</t>
+          <t>97173</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73439</t>
+          <t>82372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102150</t>
+          <t>113927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>477751</t>
+          <t>532477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>477751</t>
+          <t>532477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>477751</t>
+          <t>532477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>697100</t>
+          <t>758496</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>697100</t>
+          <t>758496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>697100</t>
+          <t>758496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1174851</t>
+          <t>1290972</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1174851</t>
+          <t>1290972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1174851</t>
+          <t>1290972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38127</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>32789</t>
+          <t>41595</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>59873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2152370</t>
+          <t>2065939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2126054</t>
+          <t>2038616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2186118</t>
+          <t>2089847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2127110</t>
+          <t>2035549</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2105424</t>
+          <t>2017671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2148939</t>
+          <t>2053417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4279479</t>
+          <t>4101488</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4240351</t>
+          <t>4067543</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4318730</t>
+          <t>4131938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>65085</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33586</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69189</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>38403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>65780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>94284</t>
+          <t>115888</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72045</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118712</t>
+          <t>140169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27040</t>
+          <t>33856</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>23170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>33599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>65360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2260471</t>
+          <t>2197562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2260471</t>
+          <t>2197562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2260471</t>
+          <t>2197562</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2209732</t>
+          <t>2137553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2209732</t>
+          <t>2137553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2209732</t>
+          <t>2137553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4470203</t>
+          <t>4335115</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4470203</t>
+          <t>4335115</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4470203</t>
+          <t>4335115</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>619633</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>608077</t>
+          <t>670919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>628689</t>
+          <t>690862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>635612</t>
+          <t>705411</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>623751</t>
+          <t>694164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>642730</t>
+          <t>713206</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1255245</t>
+          <t>1387463</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1239926</t>
+          <t>1372526</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1266668</t>
+          <t>1400369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>642966</t>
+          <t>707787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642966</t>
+          <t>707787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>642966</t>
+          <t>707787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>655951</t>
+          <t>729051</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>655951</t>
+          <t>729051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>655951</t>
+          <t>729051</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1298917</t>
+          <t>1436838</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1298917</t>
+          <t>1436838</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1298917</t>
+          <t>1436838</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41577</t>
+          <t>42030</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41846</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46966</t>
+          <t>53501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77450</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46974</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>55212</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>61329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82613</t>
+          <t>97598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3176389</t>
+          <t>3196536</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3144587</t>
+          <t>3163158</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3227045</t>
+          <t>3224074</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3375852</t>
+          <t>3406599</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3346737</t>
+          <t>3379355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3409823</t>
+          <t>3429314</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6552240</t>
+          <t>6603133</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6506203</t>
+          <t>6559412</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6607123</t>
+          <t>6639982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>121619</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>101411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120299</t>
+          <t>146607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>90573</t>
+          <t>103357</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>88924</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109422</t>
+          <t>124349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>224976</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159120</t>
+          <t>199483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218560</t>
+          <t>256440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>46164</t>
+          <t>56162</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>42635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>75276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>50453</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>77760</t>
+          <t>92720</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99722</t>
+          <t>115318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3381189</t>
+          <t>3437826</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3381189</t>
+          <t>3437826</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3381189</t>
+          <t>3437826</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3562783</t>
+          <t>3625100</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3562783</t>
+          <t>3625100</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3562783</t>
+          <t>3625100</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6943971</t>
+          <t>7062925</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6943971</t>
+          <t>7062925</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6943971</t>
+          <t>7062925</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
